--- a/src/main/resources/templates/excel/formatoSeccionesSinAula.xlsx
+++ b/src/main/resources/templates/excel/formatoSeccionesSinAula.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bastards\Documents\NetBeansProjects\lamolina-pivot\src\main\resources\templates\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BE5512B-8500-43E6-81A3-2323484BB24C}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{029BDDD8-0F17-4A98-B387-4E15A56645A0}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>ANEXO SUPERIOR</t>
   </si>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t>OFICINA</t>
+  </si>
+  <si>
+    <t>HORARIO SECCIÓN</t>
   </si>
 </sst>
 </file>
@@ -427,23 +430,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A7:K7"/>
+  <dimension ref="A6:L7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="73.6640625" customWidth="1"/>
     <col min="3" max="3" width="65.109375" customWidth="1"/>
     <col min="4" max="4" width="13.5546875" customWidth="1"/>
-    <col min="5" max="5" width="19.109375" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.5546875" customWidth="1"/>
-    <col min="8" max="8" width="21.44140625" customWidth="1"/>
-    <col min="9" max="9" width="11.5546875" customWidth="1"/>
-    <col min="10" max="10" width="26.88671875" customWidth="1"/>
-    <col min="11" max="11" width="32.5546875" customWidth="1"/>
+    <col min="5" max="5" width="24.44140625" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="8" width="13.5546875" customWidth="1"/>
+    <col min="9" max="9" width="21.44140625" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" customWidth="1"/>
+    <col min="11" max="11" width="26.88671875" customWidth="1"/>
+    <col min="12" max="12" width="32.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="7" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -457,24 +462,27 @@
         <v>3</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>9</v>
       </c>
     </row>

--- a/src/main/resources/templates/excel/formatoSeccionesSinAula.xlsx
+++ b/src/main/resources/templates/excel/formatoSeccionesSinAula.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bastards\Documents\NetBeansProjects\lamolina-pivot\src\main\resources\templates\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{029BDDD8-0F17-4A98-B387-4E15A56645A0}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D05ED67-CD77-4368-A6EC-7F6240E7443E}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>ANEXO SUPERIOR</t>
   </si>
@@ -56,6 +56,9 @@
   </si>
   <si>
     <t>HORARIO SECCIÓN</t>
+  </si>
+  <si>
+    <t>CAPACIDAD</t>
   </si>
 </sst>
 </file>
@@ -430,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A6:L7"/>
+  <dimension ref="A6:M7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -443,12 +446,13 @@
     <col min="8" max="8" width="13.5546875" customWidth="1"/>
     <col min="9" max="9" width="21.44140625" customWidth="1"/>
     <col min="10" max="10" width="11.5546875" customWidth="1"/>
-    <col min="11" max="11" width="26.88671875" customWidth="1"/>
-    <col min="12" max="12" width="32.5546875" customWidth="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="12" max="12" width="26.88671875" customWidth="1"/>
+    <col min="13" max="13" width="32.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="7" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -480,9 +484,12 @@
         <v>8</v>
       </c>
       <c r="K7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="M7" s="1" t="s">
         <v>9</v>
       </c>
     </row>

--- a/src/main/resources/templates/excel/formatoSeccionesSinAula.xlsx
+++ b/src/main/resources/templates/excel/formatoSeccionesSinAula.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bastards\Documents\NetBeansProjects\lamolina-pivot\src\main\resources\templates\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D05ED67-CD77-4368-A6EC-7F6240E7443E}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{809F9F7D-C635-4924-9B23-D313F057F4B2}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -440,9 +440,9 @@
     <col min="2" max="2" width="73.6640625" customWidth="1"/>
     <col min="3" max="3" width="65.109375" customWidth="1"/>
     <col min="4" max="4" width="13.5546875" customWidth="1"/>
-    <col min="5" max="5" width="24.44140625" customWidth="1"/>
-    <col min="6" max="6" width="19.109375" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" customWidth="1"/>
+    <col min="7" max="7" width="30.33203125" customWidth="1"/>
     <col min="8" max="8" width="13.5546875" customWidth="1"/>
     <col min="9" max="9" width="21.44140625" customWidth="1"/>
     <col min="10" max="10" width="11.5546875" customWidth="1"/>
@@ -466,13 +466,13 @@
         <v>3</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>6</v>
